--- a/01-03-02/check-form-example.xlsx
+++ b/01-03-02/check-form-example.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시1 릴스 한마디" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시2 정육점·식당 대표" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시2 반찬가게 대표" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시3 직장인" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시4 프리랜서" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="진단 한 장 예시" sheetId="5" state="visible" r:id="rId5"/>
@@ -641,7 +641,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B7:B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"있음,없음,해당 없음"</formula1>
+      <formula1>"있음,없음"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -665,14 +665,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>예시 ② 정육점 · 식당 대표님 (01-03-01 예시 ①과 같은 대표님)</t>
+          <t>예시 ② 반찬가게 대표님 (01-03-01 예시 ①과 같은 대표님, 지어낸 예시)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>첫 통화에서 대표님이 말한 일 시키는 방식을 점검표에 대어 본 판정이에요.</t>
+          <t>지어낸 예시예요. 일 시키는 방식을 점검표에 대어 봤어요.</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>고기 자르는 법을 직접 보여 주며 「이렇게 이렇게 해라」</t>
+          <t>반찬 간 맞추는 법을 직접 보여 주며 「이렇게 이렇게 해라」</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
@@ -712,12 +712,12 @@
           <t>1. 목적</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr"/>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>어떤 두께·모양으로, 손실이 안 나게 자른 모습이 대표님 머릿속에만 있어요</t>
+          <t>어떤 간 세기로, 몇 g씩 담는 모습이 대표님 머릿속에만 있어요</t>
         </is>
       </c>
     </row>
@@ -742,12 +742,12 @@
           <t>3. 기준</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr"/>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
@@ -755,14 +755,14 @@
           <t>4. 마감</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>매일 하는 손질이라 마감보다 기준이 중요한 일</t>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>언제까지 몇 번 확인할지 정해 두지 않았어요</t>
         </is>
       </c>
     </row>
@@ -795,14 +795,14 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>빠진 칸: 목적·결과물 모습·기준</t>
+          <t>빠진 칸: 목적·결과물 모습·기준·마감</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>그래서 직원이 자른 고기가 대표님이 자른 것과 조금씩 달라요. 같은 만 원어치라도 개수가 달라져요.</t>
+          <t>그래서 직원이 담은 반찬 양이 대표님이 담은 것과 조금씩 달라요. 같은 한 팩이라도 양이 달라져요.</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B7:B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"있음,없음,해당 없음"</formula1>
+      <formula1>"있음,없음"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -985,7 +985,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B7:B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"있음,없음,해당 없음"</formula1>
+      <formula1>"있음,없음"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1147,7 +1147,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B7:B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"있음,없음,해당 없음"</formula1>
+      <formula1>"있음,없음"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1171,14 +1171,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>진단 한 장 예시 (유아용품 브랜드 대표님)</t>
+          <t>진단 한 장 예시 (온라인몰 대표님, 지어낸 예시)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01-01-02 예시 A와 01-02-02 예시 판 ①은 같은 대표님이에요. 앞 두 줄은 그 값을 그대로 옮겼고, 색칠한 세 줄은 예시를 완성하려고 채웠어요.</t>
+          <t>01-02-02 예시 ①과 같은 대표님이에요. 지어낸 예시예요. 앞 두 줄은 앞 양식 값을 옮겼고, 색칠한 세 줄은 예시를 완성하려고 채운 값이에요.</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>01-01-02 간소 진단서</t>
+          <t>AI 업무 시스템 진단 (레벨 등급 · 먼저 채울 칸)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>직원에게 「공구 진행 기록 정리해 둬」 · 5 / 5 (목적·결과물 모습·기준·마감·참고 자료)</t>
+          <t>직원에게 「이벤트 진행 기록 정리해 둬」 · 5 / 5 (목적·결과물 모습·기준·마감·참고 자료)</t>
         </is>
       </c>
     </row>

--- a/01-03-02/check-form-example.xlsx
+++ b/01-03-02/check-form-example.xlsx
@@ -774,12 +774,12 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>직접 보여 줌</t>
+          <t>링크나 예시는 없고 직접 보여 줬어요</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>빠진 칸: 목적·결과물 모습·기준·마감</t>
+          <t>빠진 칸: 목적·결과물 모습·기준·마감·참고 자료</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>지난번 영상 링크를 안 줌</t>
+          <t>지난번 영상 링크를 안 줬어요</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>가장 낮은 등급 · 그 영역 · 먼저 다질 칸</t>
+          <t>가장 낮은 등급 · 그 영역 · 먼저 채울 칸</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>첫 줄의 먼저 다질 칸 + 셋째 줄에서 빠진 칸을 한 줄로</t>
+          <t>첫 줄의 먼저 채울 칸 + 셋째 줄에서 빠진 칸을 한 줄로</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">

--- a/01-03-02/check-form-example.xlsx
+++ b/01-03-02/check-form-example.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시1 릴스 한마디" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시2 반찬가게 대표" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시2 카페 대표" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시3 직장인" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시4 프리랜서" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="진단 한 장 예시" sheetId="5" state="visible" r:id="rId5"/>
@@ -522,7 +522,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>「인스타 릴스 좀 기획해서 가져와 봐」</t>
+          <t>「인스타 릴스 하나 기획해서 가져와 봐」</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(B7:B11,"없음")&amp;" / 5"</f>
+        <f>IF(COUNTA(B7:B11)=0,"",COUNTIF(B7:B11,"없음")&amp;" / 5")</f>
         <v/>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -665,7 +665,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>예시 ② 반찬가게 대표님 (01-03-01 예시 ①과 같은 대표님, 지어낸 예시)</t>
+          <t>예시 ② 카페 대표님 (01-03-01 예시 ①과 같은 대표님, 지어낸 예시)</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>반찬 간 맞추는 법을 직접 보여 주며 「이렇게 이렇게 해라」</t>
+          <t>알바생에게 「마감 정리 좀 해 줘」</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>어떤 간 세기로, 몇 g씩 담는 모습이 대표님 머릿속에만 있어요</t>
+          <t>어디까지 치우면 마감이 끝인지 대표님 머릿속에만 있어요</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>언제까지 몇 번 확인할지 정해 두지 않았어요</t>
+          <t>몇 시까지 끝낼지 정해 두지 않았어요</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>링크나 예시는 없고 직접 보여 줬어요</t>
+          <t>순서표나 사진 같은 참고 자료는 없어요</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(B7:B11,"없음")&amp;" / 5"</f>
+        <f>IF(COUNTA(B7:B11)=0,"",COUNTIF(B7:B11,"없음")&amp;" / 5")</f>
         <v/>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>그래서 직원이 담은 반찬 양이 대표님이 담은 것과 조금씩 달라요. 같은 한 팩이라도 양이 달라져요.</t>
+          <t>그래서 알바생마다 마감한 뒤의 가게 모습이 조금씩 달라요.</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(B7:B11,"없음")&amp;" / 5"</f>
+        <f>IF(COUNTA(B7:B11)=0,"",COUNTIF(B7:B11,"없음")&amp;" / 5")</f>
         <v/>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(B7:B11,"없음")&amp;" / 5"</f>
+        <f>IF(COUNTA(B7:B11)=0,"",COUNTIF(B7:B11,"없음")&amp;" / 5")</f>
         <v/>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -1202,12 +1202,12 @@
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>AI 업무 시스템 진단 (레벨 등급 · 먼저 채울 칸)</t>
+          <t>AI 업무 시스템 진단 (레벨 등급 · 지금 먼저 잡을 것)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>가장 낮은 등급 · 그 영역 · 먼저 채울 칸</t>
+          <t>가장 낮은 등급 · 그 영역 · 지금 먼저 잡을 것</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>나는 가·나·다 중 __에서 멈추는 사람 · 다음엔 __부터</t>
+          <t>나는 첫 번째 · 두 번째 · 세 번째 중 __에서 멈추는 사람 · 다음엔 __부터</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>첫 줄의 먼저 채울 칸 + 셋째 줄에서 빠진 칸을 한 줄로</t>
+          <t>첫 줄의 지금 먼저 잡을 것 + 셋째 줄에서 빠진 칸을 한 줄로</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">

--- a/01-03-02/check-form-example.xlsx
+++ b/01-03-02/check-form-example.xlsx
@@ -69,7 +69,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -91,11 +91,44 @@
         <color rgb="00DCD1C1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DCD1C1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DCD1C1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DCD1C1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DCD1C1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DCD1C1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DCD1C1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -127,6 +160,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -514,6 +548,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -525,8 +560,9 @@
           <t>「인스타 릴스 하나 기획해서 가져와 봐」</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
-    </row>
+      <c r="C4" s="13" t="n"/>
+    </row>
+    <row r="5"/>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
@@ -625,6 +661,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
@@ -676,6 +713,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -687,8 +725,9 @@
           <t>알바생에게 「마감 정리 좀 해 줘」</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
-    </row>
+      <c r="C4" s="13" t="n"/>
+    </row>
+    <row r="5"/>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
@@ -799,6 +838,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
@@ -850,6 +890,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -861,8 +902,9 @@
           <t>「금요일까지 주간 보고서 초안 부탁해요」</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
-    </row>
+      <c r="C4" s="13" t="n"/>
+    </row>
+    <row r="5"/>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
@@ -1020,6 +1062,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1031,8 +1074,9 @@
           <t>외주 자막 작업자에게 「지난번처럼 자막 넣어 주세요」</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
-    </row>
+      <c r="C4" s="13" t="n"/>
+    </row>
+    <row r="5"/>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
@@ -1182,6 +1226,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1284,6 +1329,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
